--- a/Collections/USA/#USA#Commemorative#[1999-present]#circulation_quality.xlsx
+++ b/Collections/USA/#USA#Commemorative#[1999-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC1B64-7FD4-4909-A466-244E7875320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3638579B-9FDD-4982-A5F5-455675DE6DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&quot;Linkoln_Cents&quot;" sheetId="7" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="&quot;Presidential_Dollars&quot;" sheetId="1" r:id="rId6"/>
     <sheet name="&quot;Sacagawea&amp;Native_Dollars&quot;" sheetId="2" r:id="rId7"/>
     <sheet name="&quot;American_Innovation_Dollars&quot;" sheetId="3" r:id="rId8"/>
-    <sheet name="Links" sheetId="4" r:id="rId9"/>
+    <sheet name="&quot;250th Independence of USA&quot;" sheetId="10" r:id="rId9"/>
+    <sheet name="Links" sheetId="4" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'"250th Independence of USA"'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'"American_Innovation_Dollars"'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'"American_Women_Quarters"'!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'"Linkoln_Cents"'!$B$2:$G$2</definedName>
@@ -1041,8 +1043,126 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Пользователь Windows</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{6248AB1D-A80F-4E3A-9B1D-9CC017666C5E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Philadelphia mint</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{7DDF8598-11B7-4C77-B82D-A5727D20BD81}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> Denver mint</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{C54CF159-136D-47D1-BC84-3AD5FD627D71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Philadelphia mint</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{BFA9696C-61FE-4C3B-A774-FE73C95F8F61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> Denver mint</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{E00BC31B-F7C6-4CE5-83F0-4D72BD929E45}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>San Francisco mint</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="751">
   <si>
     <t>Trustees’ Garden</t>
   </si>
@@ -3250,6 +3370,51 @@
   </si>
   <si>
     <t>152,600,000</t>
+  </si>
+  <si>
+    <t>en.ucoin.net</t>
+  </si>
+  <si>
+    <t>Low convenience single table with varieties and mintages and photos</t>
+  </si>
+  <si>
+    <t>Norman Borlaug</t>
+  </si>
+  <si>
+    <t>Subtype_2#Coin_denomination</t>
+  </si>
+  <si>
+    <t>Semiquincentennial Coin and Medal Program</t>
+  </si>
+  <si>
+    <t>Liberty over Tyranny</t>
+  </si>
+  <si>
+    <t>Mayflower Compact</t>
+  </si>
+  <si>
+    <t>10¢(Dime)</t>
+  </si>
+  <si>
+    <t>25¢(Quarter)</t>
+  </si>
+  <si>
+    <t>American Revolutionary War</t>
+  </si>
+  <si>
+    <t>United States Declaration of Independence</t>
+  </si>
+  <si>
+    <t>Constitution of the United States</t>
+  </si>
+  <si>
+    <t>Gettysburg Address</t>
+  </si>
+  <si>
+    <t>Enduring Liberty</t>
+  </si>
+  <si>
+    <t>50¢(Half Dollar)</t>
   </si>
 </sst>
 </file>
@@ -3951,15 +4116,182 @@
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="95">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4521,6 +4853,15 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4535,16 +4876,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица4" displayName="Таблица4" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000003000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица4" displayName="Таблица4" ref="A1:C6" totalsRowShown="0">
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="93" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5055,7 +5396,7 @@
     <mergeCell ref="H1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:J5">
-    <cfRule type="containsText" dxfId="72" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5072,7 +5413,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="71" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5089,7 +5430,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="70" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5106,7 +5447,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="69" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5133,6 +5474,97 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="61.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="23">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>560</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>736</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>737</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{D54FC9EE-D552-43B8-B68E-A4E317028510}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K6"/>
@@ -5343,7 +5775,7 @@
     <mergeCell ref="H1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:J6">
-    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -7002,7 +7434,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:H58">
-    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="4" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9488,7 +9920,7 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="I3:J12 L48 L50:L51 I13:K58">
-    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="18" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9505,7 +9937,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K7">
-    <cfRule type="containsText" dxfId="65" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9522,7 +9954,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:K12">
-    <cfRule type="containsText" dxfId="64" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9539,12 +9971,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L47">
-    <cfRule type="containsText" dxfId="63" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:L57">
-    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L52))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9561,7 +9993,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L7">
-    <cfRule type="containsText" dxfId="61" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9590,7 +10022,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9607,7 +10039,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L58))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10347,7 +10779,7 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="H3:I17">
-    <cfRule type="containsText" dxfId="58" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10364,7 +10796,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J17">
-    <cfRule type="containsText" dxfId="57" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10381,7 +10813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:I18">
-    <cfRule type="containsText" dxfId="56" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10398,7 +10830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J18">
-    <cfRule type="containsText" dxfId="55" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10415,7 +10847,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I19">
-    <cfRule type="containsText" dxfId="54" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10432,7 +10864,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19">
-    <cfRule type="containsText" dxfId="53" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10449,7 +10881,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H20:I20">
-    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10466,7 +10898,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20">
-    <cfRule type="containsText" dxfId="51" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10483,7 +10915,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:I21">
-    <cfRule type="containsText" dxfId="50" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10500,7 +10932,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21">
-    <cfRule type="containsText" dxfId="49" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10517,7 +10949,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:I22">
-    <cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10534,7 +10966,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22">
-    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11821,7 +12253,7 @@
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:H41">
-    <cfRule type="containsText" dxfId="46" priority="6" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11838,7 +12270,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42:H42">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12649,7 +13081,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="G12:H22">
-    <cfRule type="containsText" dxfId="44" priority="74" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="74" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12666,17 +13098,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12:H22">
-    <cfRule type="cellIs" dxfId="43" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="76" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12:H22">
-    <cfRule type="cellIs" dxfId="42" priority="77" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="77" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H11 H3">
-    <cfRule type="containsText" dxfId="41" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12693,17 +13125,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H11 H3">
-    <cfRule type="cellIs" dxfId="40" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="69" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H11 H3">
-    <cfRule type="cellIs" dxfId="39" priority="70" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="70" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:H23">
-    <cfRule type="containsText" dxfId="38" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12720,17 +13152,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:H23">
-    <cfRule type="cellIs" dxfId="37" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="65" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:H23">
-    <cfRule type="cellIs" dxfId="36" priority="66" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="66" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24">
-    <cfRule type="containsText" dxfId="35" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12747,17 +13179,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24">
-    <cfRule type="cellIs" dxfId="34" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="57" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24">
-    <cfRule type="cellIs" dxfId="33" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="58" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="containsText" dxfId="32" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12774,17 +13206,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="cellIs" dxfId="31" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="53" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="cellIs" dxfId="30" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="54" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12801,17 +13233,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="cellIs" dxfId="28" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="49" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="cellIs" dxfId="27" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="50" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="26" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12828,17 +13260,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="cellIs" dxfId="25" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="45" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="cellIs" dxfId="24" priority="46" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="46" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="23" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12855,17 +13287,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" dxfId="22" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="41" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" dxfId="21" priority="42" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="42" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="20" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12882,17 +13314,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="37" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="cellIs" dxfId="18" priority="38" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="38" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="17" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12909,17 +13341,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="cellIs" dxfId="16" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="33" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="cellIs" dxfId="15" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="34" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12936,17 +13368,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="cellIs" dxfId="13" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="29" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="cellIs" dxfId="12" priority="30" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="30" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12963,7 +13395,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12980,17 +13412,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13007,12 +13439,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13920,7 +14352,9 @@
       <c r="A32" s="61">
         <v>2026</v>
       </c>
-      <c r="B32" s="62"/>
+      <c r="B32" s="62" t="s">
+        <v>738</v>
+      </c>
       <c r="C32" s="63" t="s">
         <v>517</v>
       </c>
@@ -13930,10 +14364,10 @@
       <c r="E32" s="64"/>
       <c r="F32" s="64"/>
       <c r="G32" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="9" t="str">
         <f t="shared" si="0"/>
@@ -14597,7 +15031,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:H31 G33:H59">
-    <cfRule type="containsText" dxfId="4" priority="80" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="80" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14614,7 +15048,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:H32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14637,80 +15071,378 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B232CC-3CA7-4F98-8B33-476BE2D62F40}">
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="50.6328125" style="19" customWidth="1"/>
+    <col min="3" max="4" width="33.6328125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="20" customWidth="1"/>
+    <col min="7" max="9" width="3.6328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>522</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>523</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>527</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="1" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="78"/>
+      <c r="E1" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="89"/>
+      <c r="G1" s="94" t="s">
+        <v>352</v>
+      </c>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="76"/>
+      <c r="B2" s="74" t="s">
+        <v>658</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="9" t="str">
+        <f>IF(OR(AND(G3&gt;1,G3&lt;&gt;"-"),AND(H3&gt;1,H3&lt;&gt;"-"),AND(I3&gt;1,I3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>528</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>525</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="23">
-        <v>4</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>560</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>561</v>
+      <c r="H4" s="14">
+        <v>2</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f>IF(OR(AND(G4&gt;1,G4&lt;&gt;"-"),AND(H4&gt;1,H4&lt;&gt;"-"),AND(I4&gt;1,I4&lt;&gt;"-")),"Can exchange","")</f>
+        <v>Can exchange</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <f>IF(OR(AND(G5&gt;1,G5&lt;&gt;"-"),AND(H5&gt;1,H5&lt;&gt;"-"),AND(I5&gt;1,I5&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="9" t="str">
+        <f>IF(OR(AND(G6&gt;1,G6&lt;&gt;"-"),AND(H6&gt;1,H6&lt;&gt;"-"),AND(I6&gt;1,I6&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="9" t="str">
+        <f>IF(OR(AND(G7&gt;1,G7&lt;&gt;"-"),AND(H7&gt;1,H7&lt;&gt;"-"),AND(I7&gt;1,I7&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="9" t="str">
+        <f>IF(OR(AND(G8&gt;1,G8&lt;&gt;"-"),AND(H8&gt;1,H8&lt;&gt;"-"),AND(I8&gt;1,I8&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>750</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="9" t="str">
+        <f>IF(OR(AND(G9&gt;1,G9&lt;&gt;"-"),AND(H9&gt;1,H9&lt;&gt;"-"),AND(I9&gt;1,I9&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
-  </hyperlinks>
+  <autoFilter ref="B2:F2" xr:uid="{C7B232CC-3CA7-4F98-8B33-476BE2D62F40}"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G3:H7">
+    <cfRule type="containsText" dxfId="19" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:H7">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7">
+    <cfRule type="containsText" dxfId="18" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H8">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H8">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:H9">
+    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:H9">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId5"/>
-  </tableParts>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>